--- a/Assets/Game/luban/config/general/hero.xlsx
+++ b/Assets/Game/luban/config/general/hero.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>张骞</t>
+  </si>
+  <si>
+    <t>房玄龄</t>
   </si>
 </sst>
 </file>
@@ -1439,7 +1442,7 @@
         <v>27</v>
       </c>
       <c r="D4" s="2">
-        <f>IF(B4="","",MOD(INT(B4/1000),10))</f>
+        <f t="shared" ref="D4:D14" si="0">IF(B4="","",MOD(INT(B4/1000),10))</f>
         <v>4</v>
       </c>
       <c r="E4" s="2">
@@ -1462,11 +1465,11 @@
         <v>28</v>
       </c>
       <c r="D5" s="2">
-        <f>IF(B5="","",MOD(INT(B5/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E5" s="2">
-        <f t="shared" ref="E5:E10" si="0">IF(B5="","",MOD(INT(B5/10000),10))</f>
+        <f t="shared" ref="E5:E14" si="1">IF(B5="","",MOD(INT(B5/10000),10))</f>
         <v>2</v>
       </c>
       <c r="F5" s="2" t="str">
@@ -1485,11 +1488,11 @@
         <v>29</v>
       </c>
       <c r="D6" s="2">
-        <f>IF(B6="","",MOD(INT(B6/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F6" s="2" t="str">
@@ -1502,11 +1505,11 @@
     </row>
     <row r="7" spans="1:10">
       <c r="D7" s="2" t="str">
-        <f>IF(B7="","",MOD(INT(B7/1000),10))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E7" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1518,11 +1521,11 @@
         <v>30</v>
       </c>
       <c r="D8" s="2">
-        <f>IF(B8="","",MOD(INT(B8/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="F8" s="2" t="str">
@@ -1541,11 +1544,11 @@
         <v>31</v>
       </c>
       <c r="D9" s="2">
-        <f>IF(B9="","",MOD(INT(B9/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="F9" s="2" t="str">
@@ -1564,11 +1567,11 @@
         <v>32</v>
       </c>
       <c r="D10" s="2">
-        <f>IF(B10="","",MOD(INT(B10/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="F10" s="2" t="str">
@@ -1581,11 +1584,11 @@
     </row>
     <row r="11" spans="1:10">
       <c r="D11" s="2" t="str">
-        <f>IF(B11="","",MOD(INT(B11/1000),10))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E11" s="2" t="str">
-        <f>IF(B11="","",MOD(INT(B11/10000),10))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1597,11 +1600,11 @@
         <v>33</v>
       </c>
       <c r="D12" s="2">
-        <f>IF(B12="","",MOD(INT(B12/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E12" s="2">
-        <f>IF(B12="","",MOD(INT(B12/10000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="F12" s="2" t="str">
@@ -1620,11 +1623,11 @@
         <v>34</v>
       </c>
       <c r="D13" s="2">
-        <f>IF(B13="","",MOD(INT(B13/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E13" s="2">
-        <f>IF(B13="","",MOD(INT(B13/10000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="F13" s="2" t="str">
@@ -1640,14 +1643,14 @@
         <v>7044003</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2">
-        <f>IF(B14="","",MOD(INT(B14/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E14" s="2">
-        <f>IF(B14="","",MOD(INT(B14/10000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="F14" s="2" t="str">
@@ -1659,7 +1662,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C7" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C10" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
